--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template_1.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template_1.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报销单与审批意见" sheetId="3" r:id="rId1"/>
+    <sheet name="报销单与审批意见 (2)" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$L$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'报销单与审批意见 (2)'!$A$1:$L$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="48">
   <si>
     <t xml:space="preserve"> {company}费用报销单</t>
   </si>
@@ -972,7 +974,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1098,6 +1100,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1383,6 +1397,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1492,6 +1513,153 @@
     <xdr:cxnSp>
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="10" name="直接连接符 9"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21078825" y="9112885"/>
+          <a:ext cx="3357880" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:prstClr val="black"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>309245</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3566160" cy="1071245"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1270</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>979170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>186055</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>979170</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直接连接符 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1270" y="9106535"/>
+          <a:ext cx="21111210" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:prstClr val="black"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>985520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>33655</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>985520</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直接连接符 3"/>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1941,7 +2109,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="21"/>
-      <c r="L7" s="42" t="s">
+      <c r="L7" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1961,10 +2129,10 @@
         <v>26</v>
       </c>
       <c r="I8" s="23"/>
-      <c r="J8" s="43" t="s">
+      <c r="J8" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="44"/>
+      <c r="K8" s="48"/>
       <c r="L8" s="23" t="s">
         <v>28</v>
       </c>
@@ -2137,4 +2305,362 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="20.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="34.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="28.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="1:12">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:12">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:12">
+      <c r="A4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="38"/>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:12">
+      <c r="A5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="J5" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:12">
+      <c r="A6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="17"/>
+      <c r="H6" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="40"/>
+      <c r="L6" s="41"/>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:12">
+      <c r="A7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="J7" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+    </row>
+    <row r="8" ht="99.95" customHeight="1" spans="1:12">
+      <c r="A8" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="23"/>
+      <c r="J8" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A9" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A10" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="23"/>
+      <c r="E10" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1" spans="1:12">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+    </row>
+    <row r="12" ht="90" customHeight="1" spans="1:12">
+      <c r="A12" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:12">
+      <c r="A13" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:12">
+      <c r="A14" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="37"/>
+      <c r="G14" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="37">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="A1:L3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0.984251968503937" bottom="0.984251968503937" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="32" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>